--- a/docs/Test_Cases.xlsx
+++ b/docs/Test_Cases.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8928" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$1:$H$16</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,8 +28,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -42,12 +43,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,7 +80,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -443,19 +444,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="3" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="31.95" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Test ID</t>
@@ -497,7 +497,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="28.8" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-01</t>
@@ -520,7 +520,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>FR-02, FR-04, FR-07</t>
+          <t>SRS-05, SRS-07</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -528,8 +528,16 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Not executed yet; no result recorded.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -554,7 +562,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>FR-03</t>
+          <t>SRS-07</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -562,10 +570,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Not executed yet; no result recorded.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28.8" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-03</t>
@@ -588,7 +604,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>FR-05</t>
+          <t>SRS-07</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -596,8 +612,16 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Not executed yet; no result recorded.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -622,7 +646,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>FR-06</t>
+          <t>SRS-07</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -630,10 +654,18 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Not executed yet; no result recorded.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.8" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>TC-05</t>
@@ -656,118 +688,150 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>FR-07</t>
+          <t>SRS-03, SRS-13</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>InfluxDB Data Explorer (bucket Smart_factory) shows measurement factory_esp32 with fields current, humidity, motor_speed, pressure, temperature, vibration, voltage and tags machine=machine1, source=ESP32; 20 rows returned for the last 24 hours. Evidence: docs/evidence/TC-05_influxdb_factory_esp32.png</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 / Akshat Kaushal</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28.8" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Failure handling</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Temporarily use an invalid InfluxDB token or endpoint in a safe test environment.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Receiver reports failure and does not return success for failed write.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>SRS-27, NSRS-04</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TC-06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Failure handling</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Temporarily use an invalid InfluxDB token or endpoint in a safe test environment.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Receiver reports failure and does not return success for failed write.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>NFR-03</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Not executed yet; no result recorded.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28.8" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>AI integration</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Populate all seven fields for machine1 within the freshness window.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>AI worker reads complete values and runs inference.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>SRS-10, SRS-14</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TC-07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>AI integration</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Populate all seven fields for machine1 within the freshness window.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>AI worker reads complete values and runs inference.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>FR-08, FR-09</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Not executed yet; no result recorded.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28.8" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>AI freshness</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Stop telemetry and wait until the latest records exceed the freshness window.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>AI worker waits and does not classify stale data.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>SRS-10, SRS-14</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TC-08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>AI freshness</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Stop telemetry and wait until the latest records exceed the freshness window.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>AI worker waits and does not classify stale data.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>FR-09, NFR-04</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Not executed yet; no result recorded.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -792,220 +856,276 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>FR-10, FR-12</t>
+          <t>SRS-13, SRS-14</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>InfluxDB Data Explorer (bucket Smart_factory), query on factory_ai for the last 15 minutes returned 39 rows. Written fields include ai_status (NORMAL), fault_probability (0.375) and input values (for example current 9.33, humidity 67, motor_speed 1469) with tag machine=machine1. Evidence: docs/evidence/TC-09_influxdb_factory_ai.png A second capture at 09:27 (docs/evidence/TC-09_influxdb_factory_ai_2.png) shows 155 rows in the last 15 minutes.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct 2026 / Akshat Kaushal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28.8" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TC-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Use controlled test inputs and inspect threshold branch behaviour.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Scores &lt;0.50 NORMAL; 0.50–&lt;0.80 WARNING; ≥0.80 FAULT.</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>SRS-14</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TC-10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Use controlled test inputs and inspect threshold branch behaviour.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Scores &lt;0.50 NORMAL; 0.50–&lt;0.80 WARNING; ≥0.80 FAULT.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>FR-11</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Not executed yet; no result recorded.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28.8" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Configure Grafana query for factory_esp32 temperature over last 15 minutes.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Panel displays points when matching data exists in selected time range.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>SRS-19, SRS-22</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Grafana dashboard with time range "Last 15 minutes" (refresh 5s): the ESP32 Temperature panel shows a continuous line of data points (series temperature {machine="machine1", source="ESP32"}); current, vibration and humidity panels also show data. Evidence: docs/evidence/TC-11_grafana_temperature.png</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct 2026 / Akshat Kaushal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28.8" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TC-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Configure Grafana query for factory_ai fault_probability and status.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>AI panels show records when AI worker has written data.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>SRS-19</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TC-11</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Configure Grafana query for factory_esp32 temperature over last 15 minutes.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Panel displays points when matching data exists in selected time range.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>FR-13</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Not executed yet; no result recorded.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28.8" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TC-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Search repository and Git history for tokens, passwords and .env files.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>No active secrets are committed; exposed tokens are rotated.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>NSRS-06</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>git ls-files showed no .env file tracked; git log --all -- .env returned no commits; keyword search for token/password/secret found only os.getenv references and placeholder values; firmware copy in repo uses placeholders.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31 Oct 2026 / Akshat Kaushal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28.8" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TC-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Model validation</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Evaluate model on an independent labelled dataset not used for training.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Report confusion matrix, recall, precision and false-positive rate; do not infer from training set.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>SRS-14, NSRS-03</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TC-12</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Dashboard</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Configure Grafana query for factory_ai fault_probability and status.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>AI panels show records when AI worker has written data.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>FR-12, FR-13</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Not executed yet; no result recorded.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28.8" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TC-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Hardware integration</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>After physical sensors are integrated (for example a BME680), connect them to the ESP32 and publish measured telemetry.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Measured values are received and verified; record the board, sensor model and evidence.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>SRS-01 (future work)</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TC-13</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Search repository and Git history for tokens, passwords and .env files.</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>No active secrets are committed; exposed tokens are rotated.</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>NFR-01, NFR-06</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TC-14</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Model validation</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Evaluate model on an independent labelled dataset not used for training.</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Report confusion matrix, recall, precision and false-positive rate; do not infer from training set.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>NFR-07</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TC-15</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Hardware integration</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>After firmware review, connect ESP32 and sensors and publish real telemetry.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Physical device data is received and verified; record board, sensor models and evidence.</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Future hardware scope</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Not Run</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Not executed (future work: requires physical sensors)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>N/A (not run)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H16"/>
@@ -1020,7 +1140,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
@@ -1055,7 +1175,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1085,7 +1205,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -1096,7 +1216,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>All test cases are unexecuted placeholders. Update only after collecting evidence.</t>
+          <t>Only TC-05, TC-09, TC-11 and TC-13 have been executed so far. All other test cases remain unexecuted; update only after collecting evidence.</t>
         </is>
       </c>
     </row>
